--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14969,7 +14987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15018,6 +15036,74 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0012</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0012 'KVAL  skupina A' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0013</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0013 'KVAL  skupina B' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0014</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0014 'KVAL  skupina C' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0015</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0015 'KVAL  skupina D' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -22889,7 +22975,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -28077,7 +28162,6 @@
         </is>
       </c>
     </row>
-    <row r="170"/>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
@@ -31407,7 +31491,6 @@
         </is>
       </c>
     </row>
-    <row r="243"/>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
@@ -33106,7 +33189,6 @@
         </is>
       </c>
     </row>
-    <row r="283"/>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
@@ -35542,7 +35624,6 @@
         </is>
       </c>
     </row>
-    <row r="339"/>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
@@ -39299,7 +39380,6 @@
         </is>
       </c>
     </row>
-    <row r="423"/>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
@@ -42288,7 +42368,6 @@
         </is>
       </c>
     </row>
-    <row r="493"/>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
@@ -46425,8 +46504,6 @@
         </is>
       </c>
     </row>
-    <row r="587"/>
-    <row r="588"/>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
@@ -50760,6 +50837,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0012</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1966_67_0012 'KVAL  skupina A' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0013</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1966_67_0013 'KVAL  skupina B' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0014</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1966_67_0014 'KVAL  skupina C' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0015</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1966_67_0015 'KVAL  skupina D' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14987,7 +14987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15040,14 +15040,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S1966_67_0012</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0012 'KVAL  skupina A' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15057,14 +15052,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1966_67_0013</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0013 'KVAL  skupina B' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15074,14 +15064,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1966_67_0014</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0014 'KVAL  skupina C' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15091,17 +15076,216 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1966_67_0015</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1966_67_0015 'KVAL  skupina D' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21652,12 +21836,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22539,12 +22723,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -22754,12 +22938,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22934,12 +23118,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22975,6 +23159,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -23633,12 +23818,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -26565,12 +26750,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno.</t>
+          <t>Kladno = TJ Svazarm Autoškola Kladno (Wiki D42 - registr ustavy 04/2026). **Svazarm** = Svaz pro spolupraci s armadou (vojensko-sportovni organizace). Autoskola Kladno = paralelni klub. city Kladno. || TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Svazarm Autoškola Kladno</t>
+          <t>Kladno</t>
         </is>
       </c>
     </row>
@@ -26706,12 +26891,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Potrubí = TJ Spartak Potrubí (Wiki D42 - registr ustavy 04/2026). Praha-podnik. **Potrubí Praha** = vyrobce trubek. city Praha.</t>
+          <t>Potrubí = TJ Spartak Potrubí (Wiki D42 - registr ustavy 04/2026). Praha-podnik. **Potrubí Praha** = vyrobce trubek. city Praha. || TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Potrubí</t>
+          <t>Potrubí Hospozín</t>
         </is>
       </c>
     </row>
@@ -27087,12 +27272,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -28162,6 +28347,7 @@
         </is>
       </c>
     </row>
+    <row r="170"/>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
@@ -30057,12 +30243,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30918,12 +31104,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -31491,6 +31677,7 @@
         </is>
       </c>
     </row>
+    <row r="243"/>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
@@ -32834,12 +33021,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Doplnění úředního prefixu „DSO" (Dobrovolná sportovní organizace, éra 1953+). Identity transition Slavia → Dynamo (D28). Sjednocení s B-týmem (D21 striktně). || DSO Dynamo Karlovy Vary 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - RKV Dynamo od 1953. Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Slavia Karlovy Vary (1932) -&gt; RKV Sokol Slavia Karlovy Vary (1951) -&gt; RKV Dynamo Karlovy Vary (1953) -&gt; DSO Dynamo Karlovy Vary (1956) -&gt; TJ Slavia Karlovy Vary (1965) -&gt; TJ Slavia PS Karlovy Vary (1974, PS = Pozemni stavby) -&gt; HC Slavia Karlovy Vary (1991) -&gt; HC Slavia Becherovka KV (1994) -&gt; HC Becherovka KV (1996) -&gt; HC Energie Karlovy Vary (2002-dnes). Patterns: Slavia Karlovy Vary, ZSJ Slavia KV, Dynamo Karlovy Vary. RKV = Reorganizace Krajove Vychovy?. city Karlovy Vary. || Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary.</t>
+          <t>Doplnění úředního prefixu „DSO" (Dobrovolná sportovní organizace, éra 1953+). Identity transition Slavia → Dynamo (D28). Sjednocení s B-týmem (D21 striktně). || DSO Dynamo Karlovy Vary 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - RKV Dynamo od 1953. Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Slavia Karlovy Vary (1932) -&gt; RKV Sokol Slavia Karlovy Vary (1951) -&gt; RKV Dynamo Karlovy Vary (1953) -&gt; DSO Dynamo Karlovy Vary (1956) -&gt; TJ Slavia Karlovy Vary (1965) -&gt; TJ Slavia PS Karlovy Vary (1974, PS = Pozemni stavby) -&gt; HC Slavia Karlovy Vary (1991) -&gt; HC Slavia Becherovka KV (1994) -&gt; HC Becherovka KV (1996) -&gt; HC Energie Karlovy Vary (2002-dnes). Patterns: Slavia Karlovy Vary, ZSJ Slavia KV, Dynamo Karlovy Vary. RKV = Reorganizace Krajove Vychovy?. city Karlovy Vary. || Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary. || TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Stará Role</t>
         </is>
       </c>
     </row>
@@ -33189,6 +33376,7 @@
         </is>
       </c>
     </row>
+    <row r="283"/>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
@@ -35624,6 +35812,7 @@
         </is>
       </c>
     </row>
+    <row r="339"/>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
@@ -35657,12 +35846,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -37152,12 +37341,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -39380,6 +39569,7 @@
         </is>
       </c>
     </row>
+    <row r="423"/>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
@@ -40011,12 +40201,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -41276,12 +41466,12 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno.</t>
+          <t>Brno = TJ VŠ Zemědělská Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ Zemědělská** = Vysoka skola zemedelska (dnes Mendelova univerzita - MENDELU). city Brno. || TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>VŠ Zemědělská Brno</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
@@ -42181,12 +42371,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Vranov nad Dyjí</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -42368,6 +42558,7 @@
         </is>
       </c>
     </row>
+    <row r="493"/>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
@@ -42784,12 +42975,12 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová.</t>
+          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová. || TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>Důl Zápotocký Orlová</t>
+          <t>Orlová</t>
         </is>
       </c>
     </row>
@@ -45959,12 +46150,12 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí.</t>
+          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí. || TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Ústí</t>
+          <t>Ústí u Vsetína</t>
         </is>
       </c>
     </row>
@@ -46504,6 +46695,8 @@
         </is>
       </c>
     </row>
+    <row r="587"/>
+    <row r="588"/>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
@@ -50843,11 +51036,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -50892,21 +51085,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1966_67_0012</t>
+          <t>CLUB_S1966_67_0019</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1966_67_0012 'KVAL  skupina A' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -50914,21 +51105,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1966_67_0013</t>
+          <t>CLUB_S1966_67_0040</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1966_67_0013 'KVAL  skupina B' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -50936,21 +51125,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1966_67_0014</t>
+          <t>CLUB_S1966_67_0045</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1966_67_0014 'KVAL  skupina C' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -50958,24 +51145,362 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1966_67_0015</t>
+          <t>CLUB_S1966_67_0051</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1966_67_0015 'KVAL  skupina D' (L25, parent=NODE_S1966_67_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0074</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0140</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0143</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0151</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0217</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0236</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0280</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0346</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0353</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0381</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0410</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0444</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0462</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0474</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0494</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0509</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1966_67_0579</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14987,7 +14987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15042,7 +15042,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15066,7 +15066,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15078,7 +15078,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15090,7 +15090,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15114,7 +15114,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15126,7 +15126,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15150,7 +15150,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15162,130 +15162,10 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15302,7 +15182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15361,6 +15241,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15403,6 +15288,11 @@
           <t>10 týmů, jeden stůl. Mistr: Dukla Jihlava. Sestup: VŽKG Ostrava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15450,6 +15340,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15492,6 +15387,11 @@
           <t>4 skupiny (A-D) čtyřkolově + finále (kvalifikace o I.ligu).</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15534,6 +15434,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15576,6 +15481,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15618,6 +15528,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15660,6 +15575,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15702,6 +15622,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15744,6 +15669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15786,6 +15716,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15833,6 +15768,11 @@
           <t>Kvalifikace o postup do II.ligy. Důležité poznámky: v západočeském přeboru nemohla do kvalifikace jít Škoda Plzeň B, proto šel Baník Sokolov; ve středoslovenském přeboru nemohla postoupit Banská Bystrica B, do kvalifikace šla Dubnica nad Váhom; u části výsledků kvalifikace existuje zdrojový rozpor (Kopaná-hokej vs Československý sport).</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15875,6 +15815,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15917,6 +15862,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15959,6 +15909,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16001,6 +15956,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0016</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16043,6 +16003,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0017</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16211,6 +16176,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0024</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16253,6 +16223,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16295,6 +16270,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16337,6 +16317,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0027</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16379,6 +16364,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0028</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16463,6 +16453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0030</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16505,6 +16500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0031</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16547,6 +16547,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0032</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16589,6 +16594,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0033</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16631,6 +16641,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16673,6 +16688,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16715,6 +16735,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16757,6 +16782,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0037</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16799,6 +16829,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0038</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16841,6 +16876,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0039</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16888,6 +16928,11 @@
           <t>Kvalifikace o I.B třídu</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0040</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16930,6 +16975,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0042</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16972,6 +17022,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0043</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17056,6 +17111,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0045</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17145,6 +17205,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0048</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17187,6 +17252,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0049</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17229,6 +17299,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0050</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17271,6 +17346,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0051</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17313,6 +17393,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0052</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17355,6 +17440,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0053</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17570,6 +17660,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0057</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17612,6 +17707,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0059</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17654,6 +17754,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0060</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17822,6 +17927,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0064</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17864,6 +17974,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0065</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17948,6 +18063,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0067</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18037,6 +18157,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0071</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18079,6 +18204,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0073</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18121,6 +18251,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0074</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18163,6 +18298,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0075</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18205,6 +18345,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0076</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18247,6 +18392,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0077</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18378,6 +18528,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0078</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18420,6 +18575,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0079</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18462,6 +18622,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0080</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18504,6 +18669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0081</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18640,6 +18810,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0084</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18724,6 +18899,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0086</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19018,6 +19198,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0100</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19060,6 +19245,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0101</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19233,6 +19423,11 @@
           <t>kvalifikace KP</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0107</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19448,6 +19643,11 @@
           <t>Západoslovenský krajský přebor; základní část -&gt; finálová skupina.</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0114</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19574,6 +19774,11 @@
           <t>Středoslovenský krajský přebor.</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0115</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19614,6 +19819,11 @@
       <c r="K101" t="inlineStr">
         <is>
           <t>Východoslovenský krajský přebor.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1965_66_0116</t>
         </is>
       </c>
     </row>
@@ -21836,12 +22046,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -22723,12 +22933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín. || TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Před sezonou přejmenována z VTJ Dukla Opava na VTJ Dukla Trenčín. || TJ TTS Trenčín (TTS = Trenčianske textilní strojárne, závod). Oprava city: "TTS Trenčín" → "Trenčín". prev k overeni Pavlem. || Trenčín = HK Dukla Trenčín (Wiki - registr ustavy 04/2026). Slovensky kraj. Tradicni vojensky klub. city Trenčín.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Trenčín</t>
         </is>
       </c>
     </row>
@@ -22938,12 +23148,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -23118,12 +23328,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -26891,12 +27101,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Potrubí = TJ Spartak Potrubí (Wiki D42 - registr ustavy 04/2026). Praha-podnik. **Potrubí Praha** = vyrobce trubek. city Praha. || TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Potrubí = TJ Spartak Potrubí (Wiki D42 - registr ustavy 04/2026). Praha-podnik. **Potrubí Praha** = vyrobce trubek. city Praha.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Potrubí Hospozín</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -33021,12 +33231,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Doplnění úředního prefixu „DSO" (Dobrovolná sportovní organizace, éra 1953+). Identity transition Slavia → Dynamo (D28). Sjednocení s B-týmem (D21 striktně). || DSO Dynamo Karlovy Vary 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - RKV Dynamo od 1953. Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Slavia Karlovy Vary (1932) -&gt; RKV Sokol Slavia Karlovy Vary (1951) -&gt; RKV Dynamo Karlovy Vary (1953) -&gt; DSO Dynamo Karlovy Vary (1956) -&gt; TJ Slavia Karlovy Vary (1965) -&gt; TJ Slavia PS Karlovy Vary (1974, PS = Pozemni stavby) -&gt; HC Slavia Karlovy Vary (1991) -&gt; HC Slavia Becherovka KV (1994) -&gt; HC Becherovka KV (1996) -&gt; HC Energie Karlovy Vary (2002-dnes). Patterns: Slavia Karlovy Vary, ZSJ Slavia KV, Dynamo Karlovy Vary. RKV = Reorganizace Krajove Vychovy?. city Karlovy Vary. || Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary. || TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění úředního prefixu „DSO" (Dobrovolná sportovní organizace, éra 1953+). Identity transition Slavia → Dynamo (D28). Sjednocení s B-týmem (D21 striktně). || DSO Dynamo Karlovy Vary 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - RKV Dynamo od 1953. Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Slavia Karlovy Vary (1932) -&gt; RKV Sokol Slavia Karlovy Vary (1951) -&gt; RKV Dynamo Karlovy Vary (1953) -&gt; DSO Dynamo Karlovy Vary (1956) -&gt; TJ Slavia Karlovy Vary (1965) -&gt; TJ Slavia PS Karlovy Vary (1974, PS = Pozemni stavby) -&gt; HC Slavia Karlovy Vary (1991) -&gt; HC Slavia Becherovka KV (1994) -&gt; HC Becherovka KV (1996) -&gt; HC Energie Karlovy Vary (2002-dnes). Patterns: Slavia Karlovy Vary, ZSJ Slavia KV, Dynamo Karlovy Vary. RKV = Reorganizace Krajove Vychovy?. city Karlovy Vary. || Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Slavia KV (1932) -&gt; Sokol -&gt; Slovan -&gt; Spartak Slavia KV -&gt; Lokomotiva KV -&gt; RH Karlovy Vary (Ruda hvezda) -&gt; Energie KV. KV se 1949 jmenovaly Karlovy Vary, predtim Karlovy Vary/Karlsbad. city Karlovy Vary.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Stará Role</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
     </row>
@@ -35846,12 +36056,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -37341,12 +37551,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -42371,12 +42581,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Rudá Hvězda</t>
+          <t>Vranov nad Dyjí</t>
         </is>
       </c>
     </row>
@@ -46150,12 +46360,12 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí. || TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Ústí = TJ Sokol Ústí (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Usti v CR - Usti nad Labem (Severocesky), Usti nad Orlici (Vychodocesky), Usti u Vsetina (Zlinsky/Severomoravsky). K overeni. city Ústí.</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Ústí u Vsetína</t>
+          <t>Ústí</t>
         </is>
       </c>
     </row>
@@ -51036,7 +51246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51090,12 +51300,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0019</t>
+          <t>CLUB_S1966_67_0074</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51110,12 +51320,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0040</t>
+          <t>CLUB_S1966_67_0140</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Trenčín' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51130,12 +51340,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0045</t>
+          <t>CLUB_S1966_67_0151</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51150,12 +51360,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0051</t>
+          <t>CLUB_S1966_67_0217</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51170,12 +51380,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0074</t>
+          <t>CLUB_S1966_67_0236</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51190,12 +51400,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0140</t>
+          <t>CLUB_S1966_67_0353</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Svazarm Autoškola Kladno' → 'Kladno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51210,12 +51420,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0143</t>
+          <t>CLUB_S1966_67_0410</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Potrubí' → 'Potrubí Hospozín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51230,12 +51440,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0151</t>
+          <t>CLUB_S1966_67_0444</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51250,12 +51460,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0217</t>
+          <t>CLUB_S1966_67_0462</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51270,12 +51480,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0236</t>
+          <t>CLUB_S1966_67_0474</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51290,217 +51500,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1966_67_0280</t>
+          <t>CLUB_S1966_67_0509</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Karlovy Vary' → 'Stará Role' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0346</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0353</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1965_66_0386 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0381</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0410</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0444</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0462</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0474</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VŠ Zemědělská Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0494</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0509</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1966_67_0579</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ústí' → 'Ústí u Vsetína' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -23369,7 +23369,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -28557,7 +28556,6 @@
         </is>
       </c>
     </row>
-    <row r="170"/>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
@@ -31887,7 +31885,6 @@
         </is>
       </c>
     </row>
-    <row r="243"/>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
@@ -33586,7 +33583,6 @@
         </is>
       </c>
     </row>
-    <row r="283"/>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
@@ -36022,7 +36018,6 @@
         </is>
       </c>
     </row>
-    <row r="339"/>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
@@ -39779,7 +39774,6 @@
         </is>
       </c>
     </row>
-    <row r="423"/>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
@@ -42768,7 +42762,6 @@
         </is>
       </c>
     </row>
-    <row r="493"/>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
@@ -46905,8 +46898,6 @@
         </is>
       </c>
     </row>
-    <row r="587"/>
-    <row r="588"/>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -15182,7 +15182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15244,6 +15244,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -15528,6 +15528,16 @@
           <t>NODE_S1966_67_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15542,6 +15552,14 @@
         <is>
           <t>NODE_S1965_66_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15575,6 +15593,8 @@
           <t>NODE_S1966_67_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15589,6 +15609,14 @@
         <is>
           <t>NODE_S1965_66_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -15622,6 +15650,8 @@
           <t>NODE_S1966_67_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15636,6 +15666,14 @@
         <is>
           <t>NODE_S1965_66_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16364,6 +16402,8 @@
           <t>NODE_S1966_67_0020</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16378,6 +16418,14 @@
         <is>
           <t>NODE_S1965_66_0028</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -17440,6 +17488,8 @@
           <t>NODE_S1966_67_0043</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17454,6 +17504,14 @@
         <is>
           <t>NODE_S1965_66_0053</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -17801,6 +17859,12 @@
           <t>NODE_S1966_67_0053</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NODE_S1966_67_0057</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17810,6 +17874,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -17885,6 +17957,8 @@
           <t>NODE_S1966_67_0053</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17894,6 +17968,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -18392,6 +18474,8 @@
           <t>NODE_S1966_67_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18406,6 +18490,14 @@
         <is>
           <t>NODE_S1965_66_0077</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -18439,6 +18531,8 @@
           <t>NODE_S1966_67_0064</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18448,6 +18542,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -18988,6 +19090,8 @@
           <t>NODE_S1966_67_0077</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18997,6 +19101,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -714,6 +714,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -15593,8 +15598,6 @@
           <t>NODE_S1966_67_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15650,8 +15653,6 @@
           <t>NODE_S1966_67_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16402,8 +16403,6 @@
           <t>NODE_S1966_67_0020</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17488,8 +17487,6 @@
           <t>NODE_S1966_67_0043</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17859,7 +17856,6 @@
           <t>NODE_S1966_67_0053</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>NODE_S1966_67_0057</t>
@@ -17957,8 +17953,6 @@
           <t>NODE_S1966_67_0053</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18474,8 +18468,6 @@
           <t>NODE_S1966_67_0064</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18531,8 +18523,6 @@
           <t>NODE_S1966_67_0064</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19090,8 +19080,6 @@
           <t>NODE_S1966_67_0077</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -47934,7 +47922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48126,6 +48114,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>U části výsledků kvalifikace o II.ligu existuje zdrojový rozpor (Kopaná-hokej vs Československý sport).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1966_67_FINAL.xlsx
+++ b/data/S1966_67_FINAL.xlsx
@@ -23479,6 +23479,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -28666,6 +28667,7 @@
         </is>
       </c>
     </row>
+    <row r="170"/>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
@@ -31995,6 +31997,7 @@
         </is>
       </c>
     </row>
+    <row r="243"/>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
@@ -33693,6 +33696,7 @@
         </is>
       </c>
     </row>
+    <row r="283"/>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
@@ -36128,6 +36132,7 @@
         </is>
       </c>
     </row>
+    <row r="339"/>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
@@ -39884,6 +39889,7 @@
         </is>
       </c>
     </row>
+    <row r="423"/>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
@@ -42872,6 +42878,7 @@
         </is>
       </c>
     </row>
+    <row r="493"/>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
@@ -47008,6 +47015,8 @@
         </is>
       </c>
     </row>
+    <row r="587"/>
+    <row r="588"/>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
